--- a/research/traditional_assets/database/data/croatia/croatia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_financial_svcs_non_bank_insurance.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.1351351351351351</v>
+        <v>0.07593123209169055</v>
       </c>
       <c r="H2">
-        <v>0.1351351351351351</v>
+        <v>0.07593123209169055</v>
       </c>
       <c r="I2">
-        <v>0.02972972972972973</v>
+        <v>0.04441260744985673</v>
       </c>
       <c r="J2">
-        <v>0.02576576576576577</v>
+        <v>0.02934404420794106</v>
       </c>
       <c r="K2">
-        <v>0.065</v>
+        <v>0.036</v>
       </c>
       <c r="L2">
-        <v>0.01756756756756757</v>
+        <v>0.01031518624641834</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="V2">
-        <v>0.211217183770883</v>
+        <v>0.1426991150442478</v>
       </c>
       <c r="W2">
-        <v>0.009803921568627451</v>
+        <v>0.005397301349325337</v>
       </c>
       <c r="X2">
-        <v>0.02824610541835334</v>
+        <v>0.05367355747278384</v>
       </c>
       <c r="Y2">
-        <v>-0.01844218384972589</v>
+        <v>-0.0482762561234585</v>
       </c>
       <c r="Z2">
-        <v>0.7075922738573341</v>
+        <v>0.6617368221463786</v>
       </c>
       <c r="AA2">
-        <v>0.01823165678587365</v>
+        <v>0.01941803456308576</v>
       </c>
       <c r="AB2">
-        <v>0.02860213095009385</v>
+        <v>0.05397563753471766</v>
       </c>
       <c r="AC2">
-        <v>-0.0103704741642202</v>
+        <v>-0.03455760297163189</v>
       </c>
       <c r="AD2">
-        <v>0.374</v>
+        <v>0.267</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.374</v>
+        <v>0.267</v>
       </c>
       <c r="AG2">
-        <v>-1.396</v>
+        <v>-1.023</v>
       </c>
       <c r="AH2">
-        <v>0.04272332647932373</v>
+        <v>0.02868808423767058</v>
       </c>
       <c r="AI2">
-        <v>0.05309483248154458</v>
+        <v>0.04467123975238414</v>
       </c>
       <c r="AJ2">
-        <v>-0.199885452462772</v>
+        <v>-0.1276038418360983</v>
       </c>
       <c r="AK2">
-        <v>-0.2646947288585514</v>
+        <v>-0.2182632814166845</v>
       </c>
       <c r="AL2">
-        <v>0.004</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AM2">
-        <v>-0.001</v>
+        <v>0.044</v>
       </c>
       <c r="AN2">
-        <v>1.532786885245902</v>
+        <v>0.9303135888501743</v>
       </c>
       <c r="AO2">
-        <v>27.5</v>
+        <v>2.183098591549296</v>
       </c>
       <c r="AP2">
-        <v>-5.721311475409836</v>
+        <v>-3.56445993031359</v>
       </c>
       <c r="AQ2">
-        <v>-110</v>
+        <v>3.522727272727273</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1351351351351351</v>
+        <v>0.07593123209169055</v>
       </c>
       <c r="H3">
-        <v>0.1351351351351351</v>
+        <v>0.07593123209169055</v>
       </c>
       <c r="I3">
-        <v>0.02972972972972973</v>
+        <v>0.04441260744985673</v>
       </c>
       <c r="J3">
-        <v>0.02576576576576577</v>
+        <v>0.02934404420794106</v>
       </c>
       <c r="K3">
-        <v>0.065</v>
+        <v>0.036</v>
       </c>
       <c r="L3">
-        <v>0.01756756756756757</v>
+        <v>0.01031518624641834</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="V3">
-        <v>0.211217183770883</v>
+        <v>0.1426991150442478</v>
       </c>
       <c r="W3">
-        <v>0.009803921568627451</v>
+        <v>0.005397301349325337</v>
       </c>
       <c r="X3">
-        <v>0.02824610541835334</v>
+        <v>0.05367355747278384</v>
       </c>
       <c r="Y3">
-        <v>-0.01844218384972589</v>
+        <v>-0.0482762561234585</v>
       </c>
       <c r="Z3">
-        <v>0.7075922738573341</v>
+        <v>0.6617368221463786</v>
       </c>
       <c r="AA3">
-        <v>0.01823165678587365</v>
+        <v>0.01941803456308576</v>
       </c>
       <c r="AB3">
-        <v>0.02860213095009385</v>
+        <v>0.05397563753471766</v>
       </c>
       <c r="AC3">
-        <v>-0.0103704741642202</v>
+        <v>-0.03455760297163189</v>
       </c>
       <c r="AD3">
-        <v>0.374</v>
+        <v>0.267</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.374</v>
+        <v>0.267</v>
       </c>
       <c r="AG3">
-        <v>-1.396</v>
+        <v>-1.023</v>
       </c>
       <c r="AH3">
-        <v>0.04272332647932373</v>
+        <v>0.02868808423767058</v>
       </c>
       <c r="AI3">
-        <v>0.05309483248154458</v>
+        <v>0.04467123975238414</v>
       </c>
       <c r="AJ3">
-        <v>-0.199885452462772</v>
+        <v>-0.1276038418360983</v>
       </c>
       <c r="AK3">
-        <v>-0.2646947288585514</v>
+        <v>-0.2182632814166845</v>
       </c>
       <c r="AL3">
-        <v>0.004</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AM3">
-        <v>-0.001</v>
+        <v>0.044</v>
       </c>
       <c r="AN3">
-        <v>1.532786885245902</v>
+        <v>0.9303135888501743</v>
       </c>
       <c r="AO3">
-        <v>27.5</v>
+        <v>2.183098591549296</v>
       </c>
       <c r="AP3">
-        <v>-5.721311475409836</v>
+        <v>-3.56445993031359</v>
       </c>
       <c r="AQ3">
-        <v>-110</v>
+        <v>3.522727272727273</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/croatia/croatia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/croatia/croatia_financial_svcs_non_bank_insurance.xlsx
@@ -587,32 +587,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.04769999999999999</v>
+      </c>
       <c r="G2">
-        <v>0.07593123209169055</v>
+        <v>0.08459459459459459</v>
       </c>
       <c r="H2">
-        <v>0.07593123209169055</v>
+        <v>0.08459459459459459</v>
       </c>
       <c r="I2">
-        <v>0.04441260744985673</v>
+        <v>0.01243243243243243</v>
       </c>
       <c r="J2">
-        <v>0.02934404420794106</v>
+        <v>0.01243243243243243</v>
       </c>
       <c r="K2">
-        <v>0.036</v>
+        <v>0.114</v>
       </c>
       <c r="L2">
-        <v>0.01031518624641834</v>
+        <v>0.03081081081081081</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0028328611898017</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.1754385964912281</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +627,79 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>1.29</v>
+        <v>0.403</v>
       </c>
       <c r="V2">
-        <v>0.1426991150442478</v>
+        <v>0.05708215297450426</v>
       </c>
       <c r="W2">
-        <v>0.005397301349325337</v>
+        <v>0.01996497373029773</v>
       </c>
       <c r="X2">
-        <v>0.05367355747278384</v>
+        <v>0.05703291444165626</v>
       </c>
       <c r="Y2">
-        <v>-0.0482762561234585</v>
+        <v>-0.03706794071135854</v>
       </c>
       <c r="Z2">
-        <v>0.6617368221463786</v>
+        <v>0.7892491467576793</v>
       </c>
       <c r="AA2">
-        <v>0.01941803456308576</v>
+        <v>0.009812286689419795</v>
       </c>
       <c r="AB2">
-        <v>0.05397563753471766</v>
+        <v>0.05709382793096017</v>
       </c>
       <c r="AC2">
-        <v>-0.03455760297163189</v>
+        <v>-0.04728154124154037</v>
       </c>
       <c r="AD2">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="AG2">
-        <v>-1.023</v>
+        <v>-0.137</v>
       </c>
       <c r="AH2">
-        <v>0.02868808423767058</v>
+        <v>0.03630903630903631</v>
       </c>
       <c r="AI2">
-        <v>0.04467123975238414</v>
+        <v>0.04107473749227919</v>
       </c>
       <c r="AJ2">
-        <v>-0.1276038418360983</v>
+        <v>-0.0197891087678752</v>
       </c>
       <c r="AK2">
-        <v>-0.2182632814166845</v>
+        <v>-0.02255886711674625</v>
       </c>
       <c r="AL2">
-        <v>0.07099999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="AM2">
-        <v>0.044</v>
+        <v>-0.045</v>
       </c>
       <c r="AN2">
-        <v>0.9303135888501743</v>
+        <v>1.52</v>
       </c>
       <c r="AO2">
-        <v>2.183098591549296</v>
+        <v>23</v>
       </c>
       <c r="AP2">
-        <v>-3.56445993031359</v>
+        <v>-0.7828571428571429</v>
       </c>
       <c r="AQ2">
-        <v>3.522727272727273</v>
+        <v>-1.022222222222222</v>
       </c>
     </row>
     <row r="3">
@@ -712,32 +718,35 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.04769999999999999</v>
+      </c>
       <c r="G3">
-        <v>0.07593123209169055</v>
+        <v>0.08459459459459459</v>
       </c>
       <c r="H3">
-        <v>0.07593123209169055</v>
+        <v>0.08459459459459459</v>
       </c>
       <c r="I3">
-        <v>0.04441260744985673</v>
+        <v>0.01243243243243243</v>
       </c>
       <c r="J3">
-        <v>0.02934404420794106</v>
+        <v>0.01243243243243243</v>
       </c>
       <c r="K3">
-        <v>0.036</v>
+        <v>0.114</v>
       </c>
       <c r="L3">
-        <v>0.01031518624641834</v>
+        <v>0.03081081081081081</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.0028328611898017</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.1754385964912281</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +758,79 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>1.29</v>
+        <v>0.403</v>
       </c>
       <c r="V3">
-        <v>0.1426991150442478</v>
+        <v>0.05708215297450426</v>
       </c>
       <c r="W3">
-        <v>0.005397301349325337</v>
+        <v>0.01996497373029773</v>
       </c>
       <c r="X3">
-        <v>0.05367355747278384</v>
+        <v>0.05703291444165626</v>
       </c>
       <c r="Y3">
-        <v>-0.0482762561234585</v>
+        <v>-0.03706794071135854</v>
       </c>
       <c r="Z3">
-        <v>0.6617368221463786</v>
+        <v>0.7892491467576793</v>
       </c>
       <c r="AA3">
-        <v>0.01941803456308576</v>
+        <v>0.009812286689419795</v>
       </c>
       <c r="AB3">
-        <v>0.05397563753471766</v>
+        <v>0.05709382793096017</v>
       </c>
       <c r="AC3">
-        <v>-0.03455760297163189</v>
+        <v>-0.04728154124154037</v>
       </c>
       <c r="AD3">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.267</v>
+        <v>0.266</v>
       </c>
       <c r="AG3">
-        <v>-1.023</v>
+        <v>-0.137</v>
       </c>
       <c r="AH3">
-        <v>0.02868808423767058</v>
+        <v>0.03630903630903631</v>
       </c>
       <c r="AI3">
-        <v>0.04467123975238414</v>
+        <v>0.04107473749227919</v>
       </c>
       <c r="AJ3">
-        <v>-0.1276038418360983</v>
+        <v>-0.0197891087678752</v>
       </c>
       <c r="AK3">
-        <v>-0.2182632814166845</v>
+        <v>-0.02255886711674625</v>
       </c>
       <c r="AL3">
-        <v>0.07099999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="AM3">
-        <v>0.044</v>
+        <v>-0.045</v>
       </c>
       <c r="AN3">
-        <v>0.9303135888501743</v>
+        <v>1.52</v>
       </c>
       <c r="AO3">
-        <v>2.183098591549296</v>
+        <v>23</v>
       </c>
       <c r="AP3">
-        <v>-3.56445993031359</v>
+        <v>-0.7828571428571429</v>
       </c>
       <c r="AQ3">
-        <v>3.522727272727273</v>
+        <v>-1.022222222222222</v>
       </c>
     </row>
   </sheetData>
